--- a/线材挤出机 测径 UART 通讯协议.xlsx
+++ b/线材挤出机 测径 UART 通讯协议.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\WXWork\1688855845950908\Cache\File\2026-08\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960" activeTab="1"/>
+    <workbookView windowWidth="22215" windowHeight="9780" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="数据帧格式" sheetId="1" r:id="rId1"/>
@@ -27,66 +32,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Admin</author>
-  </authors>
-  <commentList>
-    <comment ref="H7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0x00  Success
-0x01  CRC Check Failed
-0x02  Package numbers not consecutive
-0x03  Incorrect data length
-0x04  No enough memory</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0x00  Success
-0x01  CRC Check Failed
-0x02  Package numbers not consecutive
-0x03  Incorrect data length
-0x04  No enough memory</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0x00  Success
-0x01  CRC Check Failed
-0x02  Package numbers not consecutive
-0x03  Incorrect data length
-0x04  No enough memory</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="88">
   <si>
     <t>单帧数据结构 (最低9字节）</t>
   </si>
@@ -288,6 +235,23 @@
     <t>** **</t>
   </si>
   <si>
+    <t>错误码:
+typedef enum {
+  IAP_OK = 0,
+  IAP_ERR_FRAME,
+  IAP_ERR_CRC,
+  IAP_ERR_INVALID_CMD,
+  IAP_ERR_NOT_STARTED,
+  IAP_ERR_NO_SPACE,
+  IAP_ERR_WRITE_FAIL,
+  IAP_ERR_ID_NOT_MATCH,
+  IAP_ERR_FILE_SIZE,
+  IAP_ERR_PACKET_COUNT,
+  IAP_ERR_SET_FLAG_FAIL,
+  IAP_ERR_JUMP_FAIL,
+} iap_errno_t;</t>
+  </si>
+  <si>
     <t>OTA  起始帧 ACK</t>
   </si>
   <si>
@@ -333,13 +297,19 @@
     <t>OTA  结束帧 ACK</t>
   </si>
   <si>
-    <t>进入OTA更新</t>
+    <t>开始OTA更新</t>
   </si>
   <si>
     <t>0x04</t>
   </si>
   <si>
-    <t>进入OTA更新 ACK</t>
+    <t>从App切换到Bootloader</t>
+  </si>
+  <si>
+    <t>开始OTA更新 ACK</t>
+  </si>
+  <si>
+    <t>这个是App回复的</t>
   </si>
   <si>
     <t>OTA心跳</t>
@@ -348,6 +318,9 @@
     <t>0x05</t>
   </si>
   <si>
+    <t>Bootloader 定时发送心跳包</t>
+  </si>
+  <si>
     <t>终止OTA更新</t>
   </si>
   <si>
@@ -432,10 +405,10 @@
     <t>0x30</t>
   </si>
   <si>
-    <t>00 16</t>
-  </si>
-  <si>
-    <t>共计22字节：依次如下：
+    <t>00 18</t>
+  </si>
+  <si>
+    <t>共计24字节：依次如下：
 typedef struct {
     int16_t length;  // 计算偏移之后的线径值, 单位um
     int16_t raw_length;  // 原始线径值, 单位um
@@ -447,10 +420,23 @@
     uint16_t min_vo2;  // VCP1615-V2: 测量 ADC 最小值
     uint16_t max_vo2;  // VCP1615-V2: 测量 ADC 最大值
     int32_t angle_acc;  // ams5600 累计角度
+    uint16_t ams_adc;  // ams5600 当前 ADC 值
 } ccd_data_t;</t>
   </si>
   <si>
     <t>默认50ms周期</t>
+  </si>
+  <si>
+    <t>查看版本号</t>
+  </si>
+  <si>
+    <t>0x50</t>
+  </si>
+  <si>
+    <t>00 03</t>
+  </si>
+  <si>
+    <t>3个字节u8:：分别是[x].[x].[x]</t>
   </si>
 </sst>
 </file>
@@ -463,7 +449,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,13 +496,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFB58905"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -670,11 +649,6 @@
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -882,7 +856,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -956,6 +930,30 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1076,137 +1074,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1255,7 +1253,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1267,11 +1265,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1279,11 +1274,17 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1708,17 +1709,17 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:11">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:11">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="30" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:11">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="31" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1733,17 +1734,17 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="2:11">
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="32" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:11">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="2:11">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="34" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1773,7 +1774,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
@@ -1877,14 +1878,16 @@
       <c r="I6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="20"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B7" s="21" t="s">
+      <c r="J6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="22" t="s">
+    </row>
+    <row r="7" s="1" customFormat="1" ht="60" customHeight="1" spans="1:10">
+      <c r="B7" s="14" t="s">
         <v>30</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18" t="s">
@@ -1894,118 +1897,118 @@
         <v>25</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="23" t="s">
         <v>32</v>
       </c>
+      <c r="H7" s="22" t="s">
+        <v>33</v>
+      </c>
       <c r="I7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="20"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B8" s="21" t="s">
-        <v>33</v>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="60" customHeight="1" spans="1:10">
+      <c r="B8" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="23" t="s">
         <v>37</v>
       </c>
+      <c r="H8" s="22" t="s">
+        <v>38</v>
+      </c>
       <c r="I8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="20"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B9" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>30</v>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:10">
+      <c r="B9" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="23" t="s">
         <v>32</v>
       </c>
+      <c r="H9" s="22" t="s">
+        <v>33</v>
+      </c>
       <c r="I9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="20"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B10" s="21" t="s">
-        <v>39</v>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="60" customHeight="1" spans="1:10">
+      <c r="B10" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="20"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B11" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>30</v>
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="60" customHeight="1" spans="1:10">
+      <c r="B11" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="23" t="s">
         <v>32</v>
       </c>
+      <c r="H11" s="22" t="s">
+        <v>33</v>
+      </c>
       <c r="I11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="20"/>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B12" s="21"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="10"/>
       <c r="D12" s="18"/>
       <c r="E12" s="13"/>
@@ -2013,137 +2016,143 @@
       <c r="G12" s="18"/>
       <c r="H12" s="13"/>
       <c r="I12" s="18"/>
-      <c r="J12" s="20"/>
+      <c r="J12" s="26"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B13" s="21" t="s">
-        <v>44</v>
+      <c r="B13" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="20"/>
+      <c r="J13" s="26" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B14" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>30</v>
+      <c r="B14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="20"/>
+      <c r="J14" s="26" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B15" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>30</v>
+      <c r="B15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="20"/>
+      <c r="J15" s="26" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="B16" s="21" t="s">
-        <v>49</v>
+      <c r="B16" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="20"/>
+      <c r="J16" s="26"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="27"/>
       <c r="D17" s="18"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="23"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="18"/>
       <c r="J17" s="14"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B18" s="14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H18" s="22"/>
       <c r="I18" s="18" t="s">
         <v>28</v>
       </c>
@@ -2151,22 +2160,22 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B19" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H19" s="22"/>
       <c r="I19" s="18" t="s">
         <v>28</v>
       </c>
@@ -2174,22 +2183,22 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B20" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
       <c r="I20" s="18" t="s">
         <v>28</v>
       </c>
@@ -2197,22 +2206,22 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B21" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H21" s="22"/>
       <c r="I21" s="18" t="s">
         <v>28</v>
       </c>
@@ -2220,22 +2229,22 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B22" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H22" s="22"/>
       <c r="I22" s="18" t="s">
         <v>28</v>
       </c>
@@ -2243,22 +2252,22 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B23" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H23" s="22"/>
       <c r="I23" s="18" t="s">
         <v>28</v>
       </c>
@@ -2266,22 +2275,22 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B24" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H24" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H24" s="22"/>
       <c r="I24" s="18" t="s">
         <v>28</v>
       </c>
@@ -2289,22 +2298,22 @@
     </row>
     <row r="25" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B25" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H25" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H25" s="22"/>
       <c r="I25" s="18" t="s">
         <v>28</v>
       </c>
@@ -2312,22 +2321,22 @@
     </row>
     <row r="26" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B26" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H26" s="22"/>
       <c r="I26" s="18" t="s">
         <v>28</v>
       </c>
@@ -2335,22 +2344,22 @@
     </row>
     <row r="27" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B27" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H27" s="22"/>
       <c r="I27" s="18" t="s">
         <v>28</v>
       </c>
@@ -2358,22 +2367,22 @@
     </row>
     <row r="28" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B28" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H28" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H28" s="22"/>
       <c r="I28" s="18" t="s">
         <v>28</v>
       </c>
@@ -2381,22 +2390,22 @@
     </row>
     <row r="29" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B29" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H29" s="22"/>
       <c r="I29" s="18" t="s">
         <v>28</v>
       </c>
@@ -2404,22 +2413,22 @@
     </row>
     <row r="30" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B30" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H30" s="22"/>
       <c r="I30" s="18" t="s">
         <v>28</v>
       </c>
@@ -2427,22 +2436,22 @@
     </row>
     <row r="31" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B31" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D31" s="18"/>
       <c r="E31" s="13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H31" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H31" s="22"/>
       <c r="I31" s="18" t="s">
         <v>28</v>
       </c>
@@ -2450,23 +2459,23 @@
     </row>
     <row r="32" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B32" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="18"/>
       <c r="E32" s="13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>69</v>
+        <v>72</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>28</v>
@@ -2475,22 +2484,22 @@
     </row>
     <row r="33" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B33" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D33" s="18"/>
       <c r="E33" s="13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H33" s="22"/>
       <c r="I33" s="18" t="s">
         <v>28</v>
       </c>
@@ -2498,23 +2507,23 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B34" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D34" s="18"/>
       <c r="E34" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H34" s="23" t="s">
         <v>72</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>76</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>28</v>
@@ -2523,22 +2532,22 @@
     </row>
     <row r="35" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B35" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D35" s="18"/>
       <c r="E35" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H35" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H35" s="22"/>
       <c r="I35" s="18" t="s">
         <v>28</v>
       </c>
@@ -2546,22 +2555,22 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B36" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="18"/>
       <c r="E36" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H36" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H36" s="22"/>
       <c r="I36" s="18" t="s">
         <v>28</v>
       </c>
@@ -2569,22 +2578,22 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
       <c r="B37" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H37" s="23"/>
+        <v>42</v>
+      </c>
+      <c r="H37" s="22"/>
       <c r="I37" s="18" t="s">
         <v>28</v>
       </c>
@@ -2597,35 +2606,35 @@
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
-      <c r="H38" s="23"/>
+      <c r="H38" s="22"/>
       <c r="I38" s="18"/>
       <c r="J38" s="14"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="314" customHeight="1" spans="2:10">
       <c r="B39" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>30</v>
+        <v>79</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H39" s="27" t="s">
-        <v>78</v>
+        <v>81</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="I39" s="18" t="s">
         <v>28</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
@@ -2635,30 +2644,56 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
-      <c r="H40" s="23"/>
+      <c r="H40" s="22"/>
       <c r="I40" s="18"/>
       <c r="J40" s="14"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
-      <c r="B41" s="14"/>
-      <c r="C41" s="10"/>
+      <c r="B41" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="D41" s="18"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="18"/>
+      <c r="E41" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="22"/>
+      <c r="I41" s="18" t="s">
+        <v>28</v>
+      </c>
       <c r="J41" s="14"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
-      <c r="B42" s="14"/>
-      <c r="C42" s="10"/>
+      <c r="B42" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>31</v>
+      </c>
       <c r="D42" s="18"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="18"/>
+      <c r="E42" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>28</v>
+      </c>
       <c r="J42" s="14"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
@@ -2668,18 +2703,18 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
-      <c r="H43" s="23"/>
+      <c r="H43" s="22"/>
       <c r="I43" s="18"/>
       <c r="J43" s="14"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
+    <row r="44" s="1" customFormat="1" ht="31" customHeight="1" spans="2:10">
       <c r="B44" s="14"/>
       <c r="C44" s="10"/>
       <c r="D44" s="18"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
-      <c r="H44" s="23"/>
+      <c r="H44" s="22"/>
       <c r="I44" s="18"/>
       <c r="J44" s="14"/>
     </row>
@@ -2690,7 +2725,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
-      <c r="H45" s="23"/>
+      <c r="H45" s="22"/>
       <c r="I45" s="18"/>
       <c r="J45" s="14"/>
     </row>
@@ -2701,7 +2736,7 @@
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
-      <c r="H46" s="23"/>
+      <c r="H46" s="22"/>
       <c r="I46" s="18"/>
       <c r="J46" s="14"/>
     </row>
@@ -2712,7 +2747,7 @@
       <c r="E47" s="13"/>
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
-      <c r="H47" s="23"/>
+      <c r="H47" s="22"/>
       <c r="I47" s="18"/>
       <c r="J47" s="14"/>
     </row>
@@ -2723,27 +2758,60 @@
       <c r="E48" s="13"/>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
-      <c r="H48" s="23"/>
+      <c r="H48" s="22"/>
       <c r="I48" s="18"/>
       <c r="J48" s="14"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
-      <c r="B49" s="20"/>
+      <c r="B49" s="14"/>
       <c r="C49" s="10"/>
       <c r="D49" s="18"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="23"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="22"/>
       <c r="I49" s="18"/>
       <c r="J49" s="14"/>
     </row>
+    <row r="50" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
+      <c r="B50" s="14"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
+      <c r="B51" s="14"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="30" customHeight="1" spans="2:10">
+      <c r="B52" s="26"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="14"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="J6:J11"/>
     <mergeCell ref="B3:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>